--- a/output/pdf_financials_xlsx/OTC.xlsx
+++ b/output/pdf_financials_xlsx/OTC.xlsx
@@ -3440,7 +3440,7 @@
         <v>0.04535</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.507338</v>
+        <v>0.526544</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0.97021</v>
@@ -5523,7 +5523,11 @@
           <t>Warrants reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OTC.xlsx
+++ b/output/pdf_financials_xlsx/OTC.xlsx
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.405164</v>
+        <v>0.904902</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.400709</v>
+        <v>2.219947</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.778909</v>
+        <v>3.643641</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.912908</v>
+        <v>3.102783</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>2.61359</v>
+        <v>5.364296</v>
       </c>
     </row>
     <row r="11">
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.043625</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1236,7 +1236,7 @@
         <v>-3.643641</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.022158</v>
+        <v>-3.065783</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5.373327</v>
@@ -1296,7 +1296,7 @@
         <v>-3.526021</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.887854</v>
+        <v>-2.931479</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.223953</v>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.300426</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.260896</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.843116</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.602087</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
@@ -1498,16 +1498,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.300426</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.260896</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.843116</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.602087</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.91774</v>
+        <v>0.074624</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.671713</v>
+        <v>0.06962599999999999</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">

--- a/output/pdf_financials_xlsx/OTC.xlsx
+++ b/output/pdf_financials_xlsx/OTC.xlsx
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.333302</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -10228,7 +10228,11 @@
           <t>Issuance of common shares, net of issue costs (Note 6)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>0.333302</v>
       </c>
